--- a/Bao cao/MBB/MBB_Model_2026-06.xlsx
+++ b/Bao cao/MBB/MBB_Model_2026-06.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.125</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="3">
@@ -676,13 +676,13 @@
         <v>3325</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>6916.232051514553</v>
+        <v>4293.129818359497</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>7962.194754753581</v>
+        <v>4942.392832775567</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>9179.314649495553</v>
+        <v>5697.898673776243</v>
       </c>
     </row>
     <row r="5">

--- a/Bao cao/MBB/MBB_Model_2026-06.xlsx
+++ b/Bao cao/MBB/MBB_Model_2026-06.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Assumptions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_PnL" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Ratios" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="01_Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_Assumptions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03_Income_Model" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="04_PnL" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="05_Balance_Sheet" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="06_Ratios" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,11 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,33 +33,58 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001A365D"/>
       <sz val="16"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
+      <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="004A5568"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -68,11 +94,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,21 +472,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B3"/>
+  <dimension ref="B2:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>MÔ HÌNH PHÂN TÍCH TÀI CHÍNH &amp; ĐỊNH GIÁ MBB</t>
+          <t>PHÂN TÍCH CỔ PHIẾU NGÂN HÀNG: MBB</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP MBB</t>
-        </is>
+          <t>Ngân hàng Thương mại Cổ phần Quân đội</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Giá mục tiêu (VND):</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>37916</v>
       </c>
     </row>
   </sheetData>
@@ -466,70 +510,197 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Giả định</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Giá trị</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ tiêu</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>2026F</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>2027F</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>2028F</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Chi phí vốn (COE)</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>0.112</v>
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Tín dụng tăng trưởng (%)</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n"/>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="6" t="n"/>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="6" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tốc độ tăng trưởng dài hạn (g)</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>0.04</v>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Huy động tăng trưởng (%)</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>P/B Mục tiêu</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>1.3</v>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>NIM (%)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>0.0467</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>0.0578</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>0.04219999999999999</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.0391</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.0345</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.035</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Tín dụng tăng trưởng (F)</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>0.18</v>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>CIR (%)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Huy động tăng trưởng (F)</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>0.16</v>
-      </c>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Chi phí vốn CSH (COE)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n">
+        <v>0.0961</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.0961</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.0961</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Số lượng cổ phiếu</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>8396554400</v>
+      </c>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -542,178 +713,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Chỉ tiêu P&amp;L (tỷ VND)</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>2021A</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>2022A</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>2023A</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>2024A</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>2025A</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>2026E</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>2027E</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>2028E</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ tiêu</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>2026F</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>2027F</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>2028F</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Thu nhập lãi thuần (NII)</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>NII (tỷ)</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n">
         <v>26199.554</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="7" t="n">
         <v>36023.122</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="7" t="n">
         <v>38683.848</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="7" t="n">
         <v>41152.219</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F2" s="7" t="n">
         <v>51610.117</v>
       </c>
-      <c r="G2" s="5" t="n">
-        <v>47931.16857375001</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>56417.22842240101</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>66408.13096466934</v>
+      <c r="G2" s="7" t="n">
+        <v>56227.88612865</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>64169.2015788165</v>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>72567.17255929823</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Lợi nhuận sau thuế (LNST)</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>12697.075</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>17482.735</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>20676.788</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>22633.757</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>26778.939</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>34581.16025757277</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>39810.9737737679</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>45896.57324747777</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>EPS (VND)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>3133</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>3856</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>3966</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>3724</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>3325</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>4293.129818359497</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>4942.392832775567</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>5697.898673776243</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Vốn chủ sở hữu (VCSH)</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>62486.023</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>79613.219</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>96711.159</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>117059.581</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>142022.525</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>171416.5112189369</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>205255.8389266396</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>244267.9261869957</v>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Thu nhập ngoài lãi</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>10734.944</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>9569.502999999997</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>8622.214</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>14261.003</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>16082.898</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>18495.3327</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>21269.632605</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>24247.3811697</v>
       </c>
     </row>
   </sheetData>
@@ -727,240 +836,590 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Chỉ số tài chính</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>2021A</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>2022A</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>2023A</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>2024A</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>2025A</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>2026E</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>2027E</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>2028E</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ tiêu</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>2026F</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>2027F</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>2028F</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Thu nhập lãi thuần (NII)</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>26199.554</v>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>36023.122</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>38683.848</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>41152.219</v>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>51610.117</v>
+      </c>
+      <c r="G2" s="7">
+        <f>'03_Income_Model'!G2</f>
+        <v/>
+      </c>
+      <c r="H2" s="7">
+        <f>'03_Income_Model'!H2</f>
+        <v/>
+      </c>
+      <c r="I2" s="7">
+        <f>'03_Income_Model'!I2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Tổng thu nhập hoạt động (TOI)</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>36934.498</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>45592.625</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>47306.062</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>55413.222</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>67693.015</v>
+      </c>
+      <c r="G3" s="7">
+        <f>SUM(G2+'03_Income_Model'!G3)</f>
+        <v/>
+      </c>
+      <c r="H3" s="7">
+        <f>SUM(H2+'03_Income_Model'!H3)</f>
+        <v/>
+      </c>
+      <c r="I3" s="7">
+        <f>SUM(I2+'03_Income_Model'!I3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Lợi nhuận trước dự phòng (PPOP)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>24557.31</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>30776.997</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>32393.121</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>38405.972</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>48011.862</v>
+      </c>
+      <c r="G4" s="7">
+        <f>G3*(1-'02_Assumptions'!G5)</f>
+        <v/>
+      </c>
+      <c r="H4" s="7">
+        <f>H3*(1-'02_Assumptions'!H5)</f>
+        <v/>
+      </c>
+      <c r="I4" s="7">
+        <f>I3*(1-'02_Assumptions'!I5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>LNST (NPAT)</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>13221.437</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>18155.185</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>21053.792</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>22951.264</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>27382.978</v>
+      </c>
+      <c r="G5" s="7">
+        <f>G4-(('05_Balance_Sheet'!G3)*'02_Assumptions'!G4)</f>
+        <v/>
+      </c>
+      <c r="H5" s="7">
+        <f>H4-(('05_Balance_Sheet'!H3)*'02_Assumptions'!H4)</f>
+        <v/>
+      </c>
+      <c r="I5" s="7">
+        <f>I4-(('05_Balance_Sheet'!I3)*'02_Assumptions'!I4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>EPS (VND)</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>1574.626492028683</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>2162.218469042492</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>2507.432334387067</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>2733.414553950844</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>3261.216053099114</v>
+      </c>
+      <c r="G6" s="7">
+        <f>G5*1e9/'02_Assumptions'!$B$7</f>
+        <v/>
+      </c>
+      <c r="H6" s="7">
+        <f>H5*1e9/'02_Assumptions'!$B$7</f>
+        <v/>
+      </c>
+      <c r="I6" s="7">
+        <f>I5*1e9/'02_Assumptions'!$B$7</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ tiêu</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>2026F</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>2027F</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>2028F</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Tổng tài sản</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>607140.419</v>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>728532.373</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>944953.64</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>1128801.062</v>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>1615763.927</v>
+      </c>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Cho vay khách hàng</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>354797.094</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>448598.622</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>599579.267</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>765047.985</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>1070868.777</v>
+      </c>
+      <c r="G3" s="7">
+        <f>F3*(1+'02_Assumptions'!G2)</f>
+        <v/>
+      </c>
+      <c r="H3" s="7">
+        <f>G3*(1+'02_Assumptions'!H2)</f>
+        <v/>
+      </c>
+      <c r="I3" s="7">
+        <f>H3*(1+'02_Assumptions'!I2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Tiền gửi khách hàng</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>384692.155</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>443605.638</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>567532.577</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>714154.4790000001</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>921368.132</v>
+      </c>
+      <c r="G4" s="7">
+        <f>F4*(1+'02_Assumptions'!G3)</f>
+        <v/>
+      </c>
+      <c r="H4" s="7">
+        <f>G4*(1+'02_Assumptions'!H3)</f>
+        <v/>
+      </c>
+      <c r="I4" s="7">
+        <f>H4*(1+'02_Assumptions'!I3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Vốn chủ sở hữu (VCSH)</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>62486.023</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>79613.219</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>96711.159</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>117059.581</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>142022.525</v>
+      </c>
+      <c r="G5" s="7">
+        <f>F5+'04_PnL'!G5*0.7</f>
+        <v/>
+      </c>
+      <c r="H5" s="7">
+        <f>G5+'04_PnL'!H5*0.7</f>
+        <v/>
+      </c>
+      <c r="I5" s="7">
+        <f>H5+'04_PnL'!I5*0.7</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ tiêu</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>2026F</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>2027F</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>2028F</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>NIM (%)</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n">
-        <v>0.0432</v>
-      </c>
-      <c r="C2" s="7" t="n">
-        <v>0.0494</v>
-      </c>
-      <c r="D2" s="7" t="n">
-        <v>0.0409</v>
-      </c>
-      <c r="E2" s="7" t="n">
-        <v>0.0365</v>
-      </c>
-      <c r="F2" s="7" t="n">
-        <v>0.0319</v>
-      </c>
-      <c r="G2" s="7" t="n">
-        <v>0.0265</v>
-      </c>
-      <c r="H2" s="7" t="n">
-        <v>0.0278</v>
-      </c>
-      <c r="I2" s="7" t="n">
-        <v>0.0293</v>
+      <c r="B2" s="5">
+        <f>'04_PnL'!B2/'05_Balance_Sheet'!B2</f>
+        <v/>
+      </c>
+      <c r="C2" s="5">
+        <f>'04_PnL'!C2/'05_Balance_Sheet'!C2</f>
+        <v/>
+      </c>
+      <c r="D2" s="5">
+        <f>'04_PnL'!D2/'05_Balance_Sheet'!D2</f>
+        <v/>
+      </c>
+      <c r="E2" s="5">
+        <f>'04_PnL'!E2/'05_Balance_Sheet'!E2</f>
+        <v/>
+      </c>
+      <c r="F2" s="5">
+        <f>'04_PnL'!F2/'05_Balance_Sheet'!F2</f>
+        <v/>
+      </c>
+      <c r="G2" s="5">
+        <f>'04_PnL'!G2/'05_Balance_Sheet'!G2</f>
+        <v/>
+      </c>
+      <c r="H2" s="5">
+        <f>'04_PnL'!H2/'05_Balance_Sheet'!H2</f>
+        <v/>
+      </c>
+      <c r="I2" s="5">
+        <f>'04_PnL'!I2/'05_Balance_Sheet'!I2</f>
+        <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>ROE (%)</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
-        <v>0.2032</v>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>0.2196</v>
-      </c>
-      <c r="D3" s="7" t="n">
-        <v>0.2138</v>
-      </c>
-      <c r="E3" s="7" t="n">
-        <v>0.1934</v>
-      </c>
-      <c r="F3" s="7" t="n">
-        <v>0.1886</v>
-      </c>
-      <c r="G3" s="7" t="n">
-        <v>0.2017</v>
-      </c>
-      <c r="H3" s="7" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="I3" s="7" t="n">
-        <v>0.1879</v>
+      <c r="B3" s="5">
+        <f>'04_PnL'!B5/'05_Balance_Sheet'!B5</f>
+        <v/>
+      </c>
+      <c r="C3" s="5">
+        <f>'04_PnL'!C5/'05_Balance_Sheet'!C5</f>
+        <v/>
+      </c>
+      <c r="D3" s="5">
+        <f>'04_PnL'!D5/'05_Balance_Sheet'!D5</f>
+        <v/>
+      </c>
+      <c r="E3" s="5">
+        <f>'04_PnL'!E5/'05_Balance_Sheet'!E5</f>
+        <v/>
+      </c>
+      <c r="F3" s="5">
+        <f>'04_PnL'!F5/'05_Balance_Sheet'!F5</f>
+        <v/>
+      </c>
+      <c r="G3" s="5">
+        <f>'04_PnL'!G5/'05_Balance_Sheet'!G5</f>
+        <v/>
+      </c>
+      <c r="H3" s="5">
+        <f>'04_PnL'!H5/'05_Balance_Sheet'!H5</f>
+        <v/>
+      </c>
+      <c r="I3" s="5">
+        <f>'04_PnL'!I5/'05_Balance_Sheet'!I5</f>
+        <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>ROA (%)</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
-        <v>0.0209</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>0.0219</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>0.0201</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>0.0166</v>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>0.0191</v>
-      </c>
-      <c r="H4" s="7" t="n">
-        <v>0.0196</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>0.0202</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>LDR (%)</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>0.7857</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>0.8305</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>0.9074</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>0.966</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>0.9826</v>
-      </c>
-      <c r="H5" s="7" t="n">
-        <v>0.9996</v>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>1.0168</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CASA (%)</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Tỷ lệ nợ xấu NPL (%)</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>-0.0247</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>-0.0267</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>-0.0191</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>-0.0152</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>-0.0123</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="H7" s="7" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="I7" s="7" t="n">
-        <v>0.012</v>
+      <c r="B4" s="5">
+        <f>'04_PnL'!B5/'05_Balance_Sheet'!B2</f>
+        <v/>
+      </c>
+      <c r="C4" s="5">
+        <f>'04_PnL'!C5/'05_Balance_Sheet'!C2</f>
+        <v/>
+      </c>
+      <c r="D4" s="5">
+        <f>'04_PnL'!D5/'05_Balance_Sheet'!D2</f>
+        <v/>
+      </c>
+      <c r="E4" s="5">
+        <f>'04_PnL'!E5/'05_Balance_Sheet'!E2</f>
+        <v/>
+      </c>
+      <c r="F4" s="5">
+        <f>'04_PnL'!F5/'05_Balance_Sheet'!F2</f>
+        <v/>
+      </c>
+      <c r="G4" s="5">
+        <f>'04_PnL'!G5/'05_Balance_Sheet'!G2</f>
+        <v/>
+      </c>
+      <c r="H4" s="5">
+        <f>'04_PnL'!H5/'05_Balance_Sheet'!H2</f>
+        <v/>
+      </c>
+      <c r="I4" s="5">
+        <f>'04_PnL'!I5/'05_Balance_Sheet'!I2</f>
+        <v/>
       </c>
     </row>
   </sheetData>
